--- a/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
@@ -504,10 +504,10 @@
         <v>10000</v>
       </c>
       <c r="H2">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="I2">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -533,10 +533,10 @@
         <v>10000</v>
       </c>
       <c r="H3">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="I3">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -562,10 +562,10 @@
         <v>10000</v>
       </c>
       <c r="H4">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="I4">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -591,10 +591,10 @@
         <v>10000</v>
       </c>
       <c r="H5">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="I5">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -620,10 +620,10 @@
         <v>10000</v>
       </c>
       <c r="H6">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="I6">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -649,10 +649,10 @@
         <v>10000</v>
       </c>
       <c r="H7">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="I7">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -678,10 +678,10 @@
         <v>10000</v>
       </c>
       <c r="H8">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="I8">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -707,10 +707,10 @@
         <v>10000</v>
       </c>
       <c r="H9">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="I9">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -736,10 +736,10 @@
         <v>10000</v>
       </c>
       <c r="H10">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="I10">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -765,10 +765,10 @@
         <v>10000</v>
       </c>
       <c r="H11">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="I11">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -794,7 +794,7 @@
         <v>10000</v>
       </c>
       <c r="H12">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="I12">
         <v>61.6</v>
@@ -823,10 +823,10 @@
         <v>10000</v>
       </c>
       <c r="H13">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="I13">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
@@ -495,19 +495,19 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F2">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G2">
         <v>10000</v>
       </c>
       <c r="H2">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="I2">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -524,19 +524,19 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F3">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G3">
         <v>10000</v>
       </c>
       <c r="H3">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="I3">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -553,19 +553,19 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F4">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G4">
         <v>10000</v>
       </c>
       <c r="H4">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="I4">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -582,19 +582,19 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F5">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G5">
         <v>10000</v>
       </c>
       <c r="H5">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="I5">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -611,19 +611,19 @@
         <v>15</v>
       </c>
       <c r="E6">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F6">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G6">
         <v>10000</v>
       </c>
       <c r="H6">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="I6">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -640,19 +640,19 @@
         <v>18</v>
       </c>
       <c r="E7">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F7">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G7">
         <v>10000</v>
       </c>
       <c r="H7">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="I7">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -678,10 +678,10 @@
         <v>10000</v>
       </c>
       <c r="H8">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="I8">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -707,10 +707,10 @@
         <v>10000</v>
       </c>
       <c r="H9">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="I9">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -736,10 +736,10 @@
         <v>10000</v>
       </c>
       <c r="H10">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="I10">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -765,10 +765,10 @@
         <v>10000</v>
       </c>
       <c r="H11">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="I11">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -794,10 +794,10 @@
         <v>10000</v>
       </c>
       <c r="H12">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="I12">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -823,10 +823,10 @@
         <v>10000</v>
       </c>
       <c r="H13">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="I13">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
@@ -43,7 +43,7 @@
     <t>pct_aceitacao</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Jardim(1981-1994)</t>
+    <t>NN_CMSY_Jardim (1999)</t>
   </si>
   <si>
     <t>NN_CMSY</t>
@@ -55,7 +55,7 @@
     <t>Jardim (1999)</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Santos(2005-2018)</t>
+    <t>NN_CMSY_Santos (2018)</t>
   </si>
   <si>
     <t>M_Santos(2005-2018)</t>
@@ -64,7 +64,7 @@
     <t>Santos (2018)</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Vieira(1988-2018)</t>
+    <t>NN_CMSY_Vieira (2019)</t>
   </si>
   <si>
     <t>M_Vieira(1988-2018)</t>
@@ -73,40 +73,40 @@
     <t>Vieira (2019)</t>
   </si>
   <si>
-    <t>zBRT_M_Jardim(1981-1994)</t>
+    <t>zBRT_Jardim (1999)</t>
   </si>
   <si>
     <t>zBRT</t>
   </si>
   <si>
-    <t>zBRT_M_Santos(2005-2018)</t>
-  </si>
-  <si>
-    <t>zBRT_M_Vieira(1988-2018)</t>
-  </si>
-  <si>
-    <t>Target_switch_M_Jardim(1981-1994)</t>
+    <t>zBRT_Santos (2018)</t>
+  </si>
+  <si>
+    <t>zBRT_Vieira (2019)</t>
+  </si>
+  <si>
+    <t>Target_switch_Jardim (1999)</t>
   </si>
   <si>
     <t>Target_switch</t>
   </si>
   <si>
-    <t>Target_switch_M_Santos(2005-2018)</t>
-  </si>
-  <si>
-    <t>Target_switch_M_Vieira(1988-2018)</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_M_Jardim(1981-1994)</t>
+    <t>Target_switch_Santos (2018)</t>
+  </si>
+  <si>
+    <t>Target_switch_Vieira (2019)</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Jardim (1999)</t>
   </si>
   <si>
     <t>Uninformative_bk</t>
   </si>
   <si>
-    <t>Uninformative_bk_M_Santos(2005-2018)</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_M_Vieira(1988-2018)</t>
+    <t>Uninformative_bk_Santos (2018)</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Vieira (2019)</t>
   </si>
 </sst>
 </file>
@@ -495,19 +495,19 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F2">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G2">
         <v>10000</v>
       </c>
       <c r="H2">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="I2">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -524,19 +524,19 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F3">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G3">
         <v>10000</v>
       </c>
       <c r="H3">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="I3">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -553,19 +553,19 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F4">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G4">
         <v>10000</v>
       </c>
       <c r="H4">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -585,16 +585,16 @@
         <v>0.01</v>
       </c>
       <c r="F5">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G5">
         <v>10000</v>
       </c>
       <c r="H5">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -614,16 +614,16 @@
         <v>0.01</v>
       </c>
       <c r="F6">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G6">
         <v>10000</v>
       </c>
       <c r="H6">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="I6">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -643,16 +643,16 @@
         <v>0.01</v>
       </c>
       <c r="F7">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G7">
         <v>10000</v>
       </c>
       <c r="H7">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="I7">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -669,19 +669,19 @@
         <v>12</v>
       </c>
       <c r="E8">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F8">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G8">
         <v>10000</v>
       </c>
       <c r="H8">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="I8">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -698,19 +698,19 @@
         <v>15</v>
       </c>
       <c r="E9">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F9">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G9">
         <v>10000</v>
       </c>
       <c r="H9">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="I9">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -727,19 +727,19 @@
         <v>18</v>
       </c>
       <c r="E10">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F10">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
         <v>10000</v>
       </c>
       <c r="H10">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="I10">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -765,10 +765,10 @@
         <v>10000</v>
       </c>
       <c r="H11">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="I11">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -794,10 +794,10 @@
         <v>10000</v>
       </c>
       <c r="H12">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="I12">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -823,10 +823,10 @@
         <v>10000</v>
       </c>
       <c r="H13">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="I13">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
@@ -504,7 +504,7 @@
         <v>10000</v>
       </c>
       <c r="H2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I2">
         <v>1.3</v>
@@ -533,10 +533,10 @@
         <v>10000</v>
       </c>
       <c r="H3">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="I3">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -562,10 +562,10 @@
         <v>10000</v>
       </c>
       <c r="H4">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I4">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -620,10 +620,10 @@
         <v>10000</v>
       </c>
       <c r="H6">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="I6">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -649,10 +649,10 @@
         <v>10000</v>
       </c>
       <c r="H7">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="I7">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -678,10 +678,10 @@
         <v>10000</v>
       </c>
       <c r="H8">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="I8">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -707,10 +707,10 @@
         <v>10000</v>
       </c>
       <c r="H9">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="I9">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -736,10 +736,10 @@
         <v>10000</v>
       </c>
       <c r="H10">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="I10">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -765,10 +765,10 @@
         <v>10000</v>
       </c>
       <c r="H11">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="I11">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -794,10 +794,10 @@
         <v>10000</v>
       </c>
       <c r="H12">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="I12">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -823,10 +823,10 @@
         <v>10000</v>
       </c>
       <c r="H13">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="I13">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_aceitacao_dbsra_macarellus.xlsx
@@ -504,10 +504,10 @@
         <v>10000</v>
       </c>
       <c r="H2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I2">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -533,10 +533,10 @@
         <v>10000</v>
       </c>
       <c r="H3">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="I3">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -562,10 +562,10 @@
         <v>10000</v>
       </c>
       <c r="H4">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I4">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -585,16 +585,16 @@
         <v>0.01</v>
       </c>
       <c r="F5">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G5">
         <v>10000</v>
       </c>
       <c r="H5">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="I5">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -614,16 +614,16 @@
         <v>0.01</v>
       </c>
       <c r="F6">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G6">
         <v>10000</v>
       </c>
       <c r="H6">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -643,16 +643,16 @@
         <v>0.01</v>
       </c>
       <c r="F7">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G7">
         <v>10000</v>
       </c>
       <c r="H7">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="I7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -678,10 +678,10 @@
         <v>10000</v>
       </c>
       <c r="H8">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="I8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -707,7 +707,7 @@
         <v>10000</v>
       </c>
       <c r="H9">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="I9">
         <v>9.199999999999999</v>
@@ -736,7 +736,7 @@
         <v>10000</v>
       </c>
       <c r="H10">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="I10">
         <v>5.9</v>
@@ -765,10 +765,10 @@
         <v>10000</v>
       </c>
       <c r="H11">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="I11">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -794,10 +794,10 @@
         <v>10000</v>
       </c>
       <c r="H12">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="I12">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -823,10 +823,10 @@
         <v>10000</v>
       </c>
       <c r="H13">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="I13">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
   </sheetData>
